--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.56367805352266</v>
+        <v>9.191597683697433</v>
       </c>
       <c r="D2" t="n">
-        <v>57.50778095388525</v>
+        <v>9.345014405006355</v>
       </c>
       <c r="E2" t="n">
-        <v>3.163091584028785</v>
+        <v>0.5140023824046778</v>
       </c>
       <c r="F2" t="n">
-        <v>2.710155822455264</v>
+        <v>0.4404003211489804</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.98868412509714</v>
+        <v>10.23566117032829</v>
       </c>
       <c r="D3" t="n">
-        <v>62.84551949323085</v>
+        <v>10.21239691765001</v>
       </c>
       <c r="E3" t="n">
-        <v>3.163091584028785</v>
+        <v>0.5140023824046778</v>
       </c>
       <c r="F3" t="n">
-        <v>2.710155822455264</v>
+        <v>0.4404003211489804</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.52619980865853</v>
+        <v>10.32300746890701</v>
       </c>
       <c r="D4" t="n">
-        <v>63.5947873014318</v>
+        <v>10.33415293648267</v>
       </c>
       <c r="E4" t="n">
-        <v>3.163091584028785</v>
+        <v>0.5140023824046778</v>
       </c>
       <c r="F4" t="n">
-        <v>2.710155822455264</v>
+        <v>0.4404003211489804</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
